--- a/data/production/production_2026-W37.xlsx
+++ b/data/production/production_2026-W37.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -483,22 +483,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AU-772324</t>
+          <t>CM-473253</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Leah Novak</t>
+          <t>Alma Ashby</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1307.74</v>
+        <v>5040.61</v>
       </c>
     </row>
     <row r="5">
@@ -516,37 +516,67 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AU-489518</t>
+          <t>HO-693947</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mila Novak</t>
+          <t>James Whitfield</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>RENEWAL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>$2,499.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Luis Ortega</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AU-887856</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Maria Moreau</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Auto</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>RENEWAL</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$1,867.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1152.44</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -559,26 +589,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HO-139019</t>
+          <t>AU-647147</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Maria Duarte</t>
+          <t>James Whitfield</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1345.02</v>
+        <v>1607.75</v>
       </c>
     </row>
     <row r="8">
@@ -587,22 +617,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LF-455168</t>
+          <t>CM-966074</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Maria Novak</t>
+          <t>Elena Mbeki</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -610,45 +640,79 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>1207.49</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>$5,190.93</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Priya Raman</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LF-889136</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Owen Sorensen</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2022.97</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
         <v>46273</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Aisha Bello</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>HO-143015</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Victor Castillo</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>3015.54</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grant Fowler</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AU-206599</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Grace Albright</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> New</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>$1,369.72</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -656,31 +720,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LF-468727</t>
+          <t>AU-499652</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>James Moreau</t>
+          <t>Maria Lopez</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renewal </t>
+          <t>New</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1821.05</v>
+        <v>1812.78</v>
       </c>
     </row>
     <row r="12">
@@ -689,91 +753,123 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HO-776796</t>
+          <t>AU-972359</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Samuel Ruiz</t>
+          <t>Olivia Delgado</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home </t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RENEWAL</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>3129.2</v>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>$1,082.23</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HO-164879</t>
+          <t>AU-245949</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Theo Moreau</t>
+          <t>Elena Mbeki</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1349.01</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Luis Ortega</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HO-259375</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Elena Novak</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>2350.17</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n"/>
+      <c r="G14" t="n">
+        <v>2401.12</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HO-573866</t>
+          <t>AU-294257</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Adrian Okafor</t>
+          <t>Victor Castillo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -782,64 +878,64 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1796.2</v>
+        <v>1601.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AU-203896</t>
+          <t>AU-503409</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mila Tanaka</t>
+          <t>Caleb Whitfield</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auto </t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1236.81</v>
+        <v>2432.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AU-163491</t>
+          <t>AU-650210</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Marcus Novak</t>
+          <t>Elena Mbeki</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t xml:space="preserve">Auto </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -848,42 +944,40 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2366.76</v>
+        <v>976.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AU-204180</t>
+          <t>HO-989649</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hannah Haines</t>
+          <t>Owen Sorensen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>$1,254.17</t>
-        </is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2127.69</v>
       </c>
     </row>
     <row r="19">
@@ -892,31 +986,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luis Ortega </t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LF-327823</t>
+          <t>AU-232629</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Owen Sorensen</t>
+          <t>Mila Tanaka</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1131.51</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="20">
@@ -930,26 +1024,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AU-377304</t>
+          <t>CM-386926</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hugo Kowal</t>
+          <t>Sofia Pryor</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1548.88</v>
+        <v>5529.76</v>
       </c>
     </row>
     <row r="21">
@@ -958,31 +1052,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AU-130359</t>
+          <t>CM-613807</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ruby Sorensen</t>
+          <t>Alma Ashby</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auto </t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2293.63</v>
+        <v>2853.95</v>
       </c>
     </row>
     <row r="22">
@@ -996,17 +1090,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HO-468074</t>
+          <t>CM-240845</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ivy Okafor</t>
+          <t>James Whitfield</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1015,7 +1109,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2701.06</v>
+        <v>2642.78</v>
       </c>
     </row>
     <row r="23">
@@ -1024,55 +1118,55 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HO-986438</t>
+          <t>AU-904243</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jonah Calloway</t>
+          <t>Clara Pryor</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1310.31</v>
+        <v>1682.02</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LF-258290</t>
+          <t>AU-245423</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Clara Pryor</t>
+          <t>Samuel Ruiz</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1081,7 +1175,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1863.98</v>
+        <v>1771.63</v>
       </c>
     </row>
     <row r="25">
@@ -1095,17 +1189,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AU-397949</t>
+          <t>HO-718563</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Samuel Ruiz</t>
+          <t>Owen Kowal</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1114,7 +1208,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1041.76</v>
+        <v>2646.11</v>
       </c>
     </row>
     <row r="26">
@@ -1123,31 +1217,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aisha Bello </t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HO-194682</t>
+          <t>AU-387007</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Hugo Kowal</t>
+          <t>Victor Petrov</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3297.67</v>
+        <v>1002.38</v>
       </c>
     </row>
     <row r="27">
@@ -1156,68 +1250,68 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Luis Ortega</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AU-196126</t>
+          <t>HO-104170</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Olivia Hartley</t>
+          <t>Alma Ashby</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2352.31</v>
+        <v>1262.48</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
         <v>46275</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Maya Chen</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CM-739717</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Maria Duarte</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>luis ortega</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AU-998428</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Zoe Marsh</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auto </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>6022.99</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n"/>
+      <c r="G29" t="n">
+        <v>2147.06</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1225,33 +1319,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CM-530764</t>
+          <t>AU-167690</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Samuel Brennan</t>
+          <t>Sofia Pryor</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>$7,333.58</t>
-        </is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>981.28</v>
       </c>
     </row>
     <row r="31">
@@ -1260,22 +1352,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AU-897143</t>
+          <t>HO-464288</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Grace Albright</t>
+          <t>Olivia Delgado</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1284,64 +1376,64 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1769.88</v>
+        <v>1892.88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CM-900185</t>
+          <t>AU-219241</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Maria Novak</t>
+          <t>Hannah Haines</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t xml:space="preserve"> Auto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t xml:space="preserve"> Renewal</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>4515.7</v>
+        <v>1252.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t xml:space="preserve">Tom Becker </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AU-242254</t>
+          <t>LF-593649</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Leah Okafor</t>
+          <t>Theo Moreau</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1349,10 +1441,8 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>$2,288.12</t>
-        </is>
+      <c r="G33" t="n">
+        <v>1275.12</v>
       </c>
     </row>
     <row r="34">
@@ -1366,17 +1456,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AU-315173</t>
+          <t>AU-164044</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Adrian Okafor</t>
+          <t>Jonah Quill</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t xml:space="preserve">Auto </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1385,7 +1475,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1088.89</v>
+        <v>2123.83</v>
       </c>
     </row>
     <row r="35">
@@ -1394,31 +1484,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HO-535037</t>
+          <t>AU-325279</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Leah Okafor</t>
+          <t>James Whitfield</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t xml:space="preserve"> New</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2875.46</v>
+        <v>1059.55</v>
       </c>
     </row>
     <row r="36">
@@ -1427,65 +1517,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maya Chen </t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HO-809176</t>
+          <t>AU-367332</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Hannah Haines</t>
+          <t>James Whitfield</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1757.91</v>
+        <v>1037.79</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Priya Raman</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>HO-904711</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Mila Novak</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>2001.14</v>
-      </c>
+      <c r="A37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1493,42 +1553,75 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>priya raman</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LF-570711</t>
+          <t>CM-579161</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Victor Castillo</t>
+          <t>Grace Albright</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>6695.55</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Priya Raman</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HO-143907</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Owen Kowal</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>2252.86</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" t="inlineStr">
+      <c r="G39" t="n">
+        <v>1406.69</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>72145.03999999999</v>
+      <c r="G40" t="n">
+        <v>74307.44</v>
       </c>
     </row>
   </sheetData>
@@ -1542,7 +1635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,16 +1673,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LF-455168</t>
+          <t>AU-647147</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1160.77</v>
+        <v>1525.56</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1605,16 +1698,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HO-809176</t>
+          <t>AU-294257</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1573.79</v>
+        <v>1529.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1630,16 +1723,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AU-377304</t>
+          <t>HO-464288</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1491.86</v>
+        <v>1816.66</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1655,16 +1748,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AU-489518</t>
+          <t>CM-613807</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1857.82</v>
+        <v>2738.65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1675,21 +1768,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CM-739717</t>
+          <t>AU-232629</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6149.15</v>
+        <v>2183.23</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1705,7 +1798,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AU-242254</t>
+          <t>AU-998428</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1714,7 +1807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2230.89</v>
+        <v>1917.74</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1730,7 +1823,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HO-535037</t>
+          <t>HO-259375</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1739,7 +1832,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2625.86</v>
+        <v>2232.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1755,7 +1848,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CM-714953</t>
+          <t>CM-966074</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1764,11 +1857,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6116.41</v>
+        <v>4748.62</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lost</t>
+          <t>Renewed</t>
         </is>
       </c>
     </row>
@@ -1780,16 +1873,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CM-530764</t>
+          <t>HO-143907</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6855.09</v>
+        <v>1269.14</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1800,12 +1893,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LF-468727</t>
+          <t>LF-593649</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1814,7 +1907,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1740.78</v>
+        <v>1183.36</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1825,12 +1918,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HO-986438</t>
+          <t>HO-989649</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1839,7 +1932,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1327.26</v>
+        <v>2179.58</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1855,16 +1948,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HO-776796</t>
+          <t>AU-219241</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3112.27</v>
+        <v>1182.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1880,7 +1973,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AU-897143</t>
+          <t>AU-503409</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1889,7 +1982,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1803.6</v>
+        <v>2318.16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1900,21 +1993,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LF-570711</t>
+          <t>AU-245423</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2043.77</v>
+        <v>1725.17</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1925,21 +2018,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LF-258290</t>
+          <t>CM-473253</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1791.71</v>
+        <v>4700.97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1955,20 +2048,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HO-573866</t>
+          <t>AU-356647</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1751.86</v>
+        <v>1465.86</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
@@ -1980,7 +2073,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HO-194682</t>
+          <t>HO-693947</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1989,7 +2082,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3152.47</v>
+        <v>2310.13</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -2000,12 +2093,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HO-143015</t>
+          <t>HO-627026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2014,23 +2107,23 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2762.82</v>
+        <v>1434.19</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HO-164879</t>
+          <t>HO-104170</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2039,84 +2132,9 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2152.87</v>
+        <v>1241.79</v>
       </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>Renewed</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Grant Fowler</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>AU-309398</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1143.09</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Lost</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Grant Fowler</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>AU-772324</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1275</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Renewed</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Grant Fowler</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CM-900185</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>4352.91</v>
-      </c>
-      <c r="E23" t="inlineStr">
         <is>
           <t>Renewed</t>
         </is>
